--- a/config/universe-generated/templates/Universe.xlsx
+++ b/config/universe-generated/templates/Universe.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="270">
   <si>
     <t>@table</t>
   </si>
@@ -734,7 +734,13 @@
     <t>UniverseService</t>
   </si>
   <si>
-    <t>cfda7f55bc9d8c98</t>
+    <t>b59e6357048735cf</t>
+  </si>
+  <si>
+    <t>profile_owner</t>
+  </si>
+  <si>
+    <t>source_event_id</t>
   </si>
   <si>
     <t>currency_stable_key</t>
@@ -747,6 +753,12 @@
   </si>
   <si>
     <t>enum&lt;UniverseServiceKind&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;UniverseServiceProfileOwner&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;i32&gt;</t>
   </si>
   <si>
     <t>UniverseServiceParameter</t>
@@ -5202,21 +5214,23 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="3" width="12.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="5" customWidth="1"/>
-    <col min="9" max="11" width="12.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="5" customWidth="1"/>
+    <col min="11" max="13" width="12.7109375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5248,7 +5262,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1">
+    <row r="2" spans="1:14" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -5271,22 +5285,28 @@
         <v>232</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -5309,22 +5329,28 @@
         <v>232</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -5335,22 +5361,22 @@
         <v>22</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>60</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>22</v>
@@ -5361,8 +5387,14 @@
       <c r="L4" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
@@ -5399,8 +5431,14 @@
       <c r="L5" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -5414,23 +5452,25 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="42" customHeight="1">
+    <row r="7" spans="1:14" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -5445,15 +5485,20 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Currency, ResetBlessing, Reviver, Downloader, RespiteOffers, EnhanceBlessing, BlessingShop, CurioShop, TrailblazeBonus" promptTitle="UniverseServiceKind enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
       <formula1>"Currency,ResetBlessing,Reviver,Downloader,RespiteOffers,EnhanceBlessing,BlessingShop,CurioShop,TrailblazeBonus"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Standard, SwarmDisaster, GoldAndGears, DivergentUniverse" promptTitle="UniverseServiceProfileOwner enum" prompt="Select a value from the dropdown." sqref="E8:E1007">
+      <formula1>"Standard,SwarmDisaster,GoldAndGears,DivergentUniverse"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5475,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5497,7 +5542,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -5505,16 +5550,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5522,16 +5567,16 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5539,7 +5584,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
@@ -5624,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5648,7 +5693,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1">
@@ -5662,19 +5707,19 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>135</v>
@@ -5703,19 +5748,19 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>135</v>
@@ -5747,7 +5792,7 @@
         <v>84</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>22</v>
@@ -5902,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5924,7 +5969,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -5932,13 +5977,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5946,13 +5991,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5960,13 +6005,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6282,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6304,7 +6349,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -6312,16 +6357,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6329,16 +6374,16 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6346,7 +6391,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
@@ -6430,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6452,7 +6497,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -6460,7 +6505,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
@@ -6469,16 +6514,16 @@
         <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6486,7 +6531,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>69</v>
@@ -6495,16 +6540,16 @@
         <v>52</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>143</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6512,13 +6557,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -6527,7 +6572,7 @@
         <v>22</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>60</v>
@@ -6622,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6644,7 +6689,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -6652,7 +6697,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
@@ -6666,7 +6711,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>69</v>
@@ -6680,7 +6725,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>

--- a/config/universe-generated/templates/Universe.xlsx
+++ b/config/universe-generated/templates/Universe.xlsx
@@ -65,16 +65,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>86832c7c2b621567</t>
+    <t>8369e3d5d2be7871</t>
   </si>
   <si>
     <t>#name</t>
@@ -116,7 +116,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -149,7 +149,7 @@
     <t>UniverseWorld</t>
   </si>
   <si>
-    <t>1833253651d1d1a6</t>
+    <t>75b75cab1d9b0dd0</t>
   </si>
   <si>
     <t>profile_id</t>
@@ -191,7 +191,7 @@
     <t>UniverseDifficulty</t>
   </si>
   <si>
-    <t>8f178bfdd51d64b8</t>
+    <t>2aa79bfd0d0114aa</t>
   </si>
   <si>
     <t>world_id</t>
@@ -248,7 +248,7 @@
     <t>list</t>
   </si>
   <si>
-    <t>53e48fcfb13ef795</t>
+    <t>2f6a47be0cad3e87</t>
   </si>
   <si>
     <t>difficulty_id</t>
@@ -281,7 +281,7 @@
     <t>UniverseDomain</t>
   </si>
   <si>
-    <t>1a127d02373c9e0e</t>
+    <t>adbb2bd1f44f006a</t>
   </si>
   <si>
     <t>source_type</t>
@@ -305,7 +305,7 @@
     <t>UniverseMapNode</t>
   </si>
   <si>
-    <t>9dd13b15235490ec</t>
+    <t>94e6befd4cda00a8</t>
   </si>
   <si>
     <t>source_map_id</t>
@@ -335,7 +335,7 @@
     <t>UniverseMapEdge</t>
   </si>
   <si>
-    <t>1ae6d32376f54f27</t>
+    <t>cd837be2722dd257</t>
   </si>
   <si>
     <t>target_node_id</t>
@@ -347,7 +347,7 @@
     <t>UniverseRoom</t>
   </si>
   <si>
-    <t>b5ada0138d77f5d3</t>
+    <t>24ec45adb21901c7</t>
   </si>
   <si>
     <t>domain_id</t>
@@ -377,7 +377,7 @@
     <t>UniverseRoomContent</t>
   </si>
   <si>
-    <t>3c21c9f513006f58</t>
+    <t>36ef7c2c17c3813e</t>
   </si>
   <si>
     <t>room_id</t>
@@ -404,7 +404,7 @@
     <t>UniversePath</t>
   </si>
   <si>
-    <t>25ce81d7d088e3e9</t>
+    <t>bf71e68e85ee905f</t>
   </si>
   <si>
     <t>buff_type</t>
@@ -416,7 +416,7 @@
     <t>UniversePathBlessing</t>
   </si>
   <si>
-    <t>bbb488b0d4517c27</t>
+    <t>69eb44554483a9f1</t>
   </si>
   <si>
     <t>path_id</t>
@@ -434,7 +434,7 @@
     <t>UniverseResonance</t>
   </si>
   <si>
-    <t>d6e09ab66ac62a17</t>
+    <t>6eb859ad60999aed</t>
   </si>
   <si>
     <t>threshold</t>
@@ -470,7 +470,7 @@
     <t>UniverseResonanceParameter</t>
   </si>
   <si>
-    <t>94cf7117d2cab73a</t>
+    <t>bfb97bff333c7a40</t>
   </si>
   <si>
     <t>resonance_id</t>
@@ -488,7 +488,7 @@
     <t>UniverseBlessing</t>
   </si>
   <si>
-    <t>8479cfe550c6647c</t>
+    <t>dd301712d0f27620</t>
   </si>
   <si>
     <t>rarity</t>
@@ -509,7 +509,7 @@
     <t>UniverseBlessingPrerequisite</t>
   </si>
   <si>
-    <t>64ce040b66e5c5c9</t>
+    <t>33c9dceee0896f09</t>
   </si>
   <si>
     <t>blessing_id</t>
@@ -530,7 +530,7 @@
     <t>UniverseBlessingLevel</t>
   </si>
   <si>
-    <t>1ff35b47c14c1df5</t>
+    <t>3b25f89ff34b6f31</t>
   </si>
   <si>
     <t>range=1..2</t>
@@ -542,7 +542,7 @@
     <t>UniverseBlessingParameter</t>
   </si>
   <si>
-    <t>040f9caab3027d6c</t>
+    <t>f7c96a8b8ae5c79c</t>
   </si>
   <si>
     <t>blessing_level_id</t>
@@ -554,7 +554,7 @@
     <t>UniverseCurio</t>
   </si>
   <si>
-    <t>3ccdf0099f816b1f</t>
+    <t>332f2ec7a2d2b7e5</t>
   </si>
   <si>
     <t>initial_state_stable_key</t>
@@ -569,7 +569,7 @@
     <t>UniverseCurioState</t>
   </si>
   <si>
-    <t>d16aad4de9f50377</t>
+    <t>dfd58dbfa7180805</t>
   </si>
   <si>
     <t>curio_id</t>
@@ -614,7 +614,7 @@
     <t>UniverseCurioParameter</t>
   </si>
   <si>
-    <t>73e89d26a777287d</t>
+    <t>437d2bb30bb976a9</t>
   </si>
   <si>
     <t>curio_state_id</t>
@@ -626,7 +626,7 @@
     <t>UniverseOccurrence</t>
   </si>
   <si>
-    <t>c2a883f31a436270</t>
+    <t>ba0187f40c40ff86</t>
   </si>
   <si>
     <t>choice_graph_stable_key</t>
@@ -638,7 +638,7 @@
     <t>UniverseOccurrenceVariant</t>
   </si>
   <si>
-    <t>8b8fced2c6c96f4e</t>
+    <t>71339339353410a0</t>
   </si>
   <si>
     <t>occurrence_id</t>
@@ -665,7 +665,7 @@
     <t>UniverseOccurrenceChoice</t>
   </si>
   <si>
-    <t>269b40608465c555</t>
+    <t>4413f1179206ddcb</t>
   </si>
   <si>
     <t>variant_id</t>
@@ -698,7 +698,7 @@
     <t>UniverseOccurrenceCost</t>
   </si>
   <si>
-    <t>99988f4717345da5</t>
+    <t>3d466ceafd60e1d9</t>
   </si>
   <si>
     <t>choice_id</t>
@@ -713,7 +713,7 @@
     <t>UniverseOccurrenceOutcome</t>
   </si>
   <si>
-    <t>f9a05ceb8a2b9e0d</t>
+    <t>c7a9a46911c3509b</t>
   </si>
   <si>
     <t>kinds</t>
@@ -734,7 +734,7 @@
     <t>UniverseService</t>
   </si>
   <si>
-    <t>b59e6357048735cf</t>
+    <t>f930c76dca8bde91</t>
   </si>
   <si>
     <t>profile_owner</t>
@@ -764,7 +764,7 @@
     <t>UniverseServiceParameter</t>
   </si>
   <si>
-    <t>baebf6eae3f64a53</t>
+    <t>6aed8f1b192ff0e9</t>
   </si>
   <si>
     <t>service_id</t>
@@ -782,7 +782,7 @@
     <t>UniverseAbilityTreeNode</t>
   </si>
   <si>
-    <t>734569068a3ba709</t>
+    <t>27d98ae8b4e6377f</t>
   </si>
   <si>
     <t>important</t>
@@ -806,7 +806,7 @@
     <t>UniverseAbilityTreeEdge</t>
   </si>
   <si>
-    <t>bf18fcd9fa820bba</t>
+    <t>48127db1f3e102d4</t>
   </si>
   <si>
     <t>node_id</t>
@@ -821,7 +821,7 @@
     <t>UniverseAbilityTreeCost</t>
   </si>
   <si>
-    <t>ad749b40055ecf49</t>
+    <t>67d3008b56a4cb47</t>
   </si>
   <si>
     <t>source_item_id</t>
@@ -833,7 +833,7 @@
     <t>UniverseAbilityTreeEffect</t>
   </si>
   <si>
-    <t>571426cd36945825</t>
+    <t>be0759053e37863d</t>
   </si>
   <si>
     <t>target</t>
@@ -854,7 +854,7 @@
     <t>UniverseAbilityTreeParameter</t>
   </si>
   <si>
-    <t>ef3e509363999c92</t>
+    <t>5dcc18643aebc850</t>
   </si>
 </sst>
 </file>
